--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run9/epoch_110/per_file_predictions_epoch_110.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run9/epoch_110/per_file_predictions_epoch_110.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="492">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="496">
   <si>
     <t>Filename</t>
   </si>
@@ -808,19 +808,22 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0,1,0,1</t>
-  </si>
-  <si>
-    <t>0.9920,0.0017,0.0013,0.0005</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0.9864,0.0042,0.0023,0.0005</t>
   </si>
   <si>
     <t>0.0001,0.0001,0.0000,0.9999</t>
   </si>
   <si>
-    <t>0.9368,0.0003,0.0004,0.0451</t>
-  </si>
-  <si>
-    <t>0.2642,0.0001,0.0001,0.9043</t>
+    <t>0.9025,0.0002,0.0008,0.0811</t>
+  </si>
+  <si>
+    <t>0.0506,0.0002,0.0000,0.9857</t>
   </si>
   <si>
     <t>1.0000,0.0000,0.0000,0.0000</t>
@@ -832,664 +835,673 @@
     <t>0.9998,0.0000,0.0000,0.0001</t>
   </si>
   <si>
-    <t>0.9995,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9986,0.0009,0.0000,0.0001</t>
+    <t>0.9998,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9946,0.0048,0.0002,0.0002</t>
   </si>
   <si>
     <t>0.9998,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.7504,0.0104,0.1247,0.0006</t>
-  </si>
-  <si>
-    <t>0.0028,0.0010,0.9964,0.0004</t>
-  </si>
-  <si>
-    <t>0.6277,0.0005,0.5413,0.0000</t>
-  </si>
-  <si>
-    <t>0.0057,0.0002,0.9947,0.0004</t>
-  </si>
-  <si>
-    <t>0.9906,0.0003,0.0087,0.0002</t>
+    <t>0.9562,0.0008,0.0358,0.0002</t>
+  </si>
+  <si>
+    <t>0.0050,0.0002,0.9956,0.0002</t>
+  </si>
+  <si>
+    <t>0.9790,0.0003,0.0281,0.0000</t>
+  </si>
+  <si>
+    <t>0.1011,0.0007,0.9015,0.0011</t>
+  </si>
+  <si>
+    <t>0.9815,0.0007,0.0143,0.0003</t>
   </si>
   <si>
     <t>0.0000,1.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.0009,0.9986,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0136,0.9886,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.9993,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0386,0.0002,0.9559,0.0013</t>
-  </si>
-  <si>
-    <t>0.0011,0.0001,0.9985,0.0001</t>
-  </si>
-  <si>
-    <t>0.0015,0.0001,0.9987,0.0000</t>
-  </si>
-  <si>
-    <t>0.0043,0.0005,0.9921,0.0005</t>
-  </si>
-  <si>
-    <t>0.0054,0.0001,0.9963,0.0001</t>
-  </si>
-  <si>
-    <t>0.0008,0.0001,0.9989,0.0002</t>
-  </si>
-  <si>
-    <t>0.0007,0.0000,0.9989,0.0001</t>
-  </si>
-  <si>
-    <t>0.2004,0.8379,0.0006,0.0003</t>
-  </si>
-  <si>
-    <t>0.9200,0.0576,0.0066,0.0009</t>
-  </si>
-  <si>
-    <t>0.0012,0.0034,0.9972,0.0320</t>
-  </si>
-  <si>
-    <t>0.0031,0.8955,0.1865,0.0004</t>
-  </si>
-  <si>
-    <t>0.9932,0.0057,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9919,0.0045,0.0008,0.0003</t>
-  </si>
-  <si>
-    <t>0.9228,0.0919,0.0017,0.0001</t>
-  </si>
-  <si>
-    <t>0.0033,0.9945,0.0023,0.0001</t>
-  </si>
-  <si>
-    <t>0.0068,0.0587,0.8180,0.0117</t>
-  </si>
-  <si>
-    <t>0.0080,0.0015,0.9826,0.0024</t>
-  </si>
-  <si>
-    <t>0.0047,0.0266,0.9287,0.0086</t>
-  </si>
-  <si>
-    <t>0.0007,0.0000,0.9991,0.0001</t>
-  </si>
-  <si>
-    <t>0.0007,0.0013,0.9989,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.9978,0.0015,0.0003</t>
-  </si>
-  <si>
-    <t>0.0005,0.0004,0.9985,0.0003</t>
-  </si>
-  <si>
-    <t>0.0010,0.9515,0.0024,0.7845</t>
-  </si>
-  <si>
-    <t>0.0014,0.9960,0.0030,0.0007</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0070,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0020,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.0007,0.0075,0.9964,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0021,0.0000,0.9989,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.0004,0.9980,0.0015</t>
-  </si>
-  <si>
-    <t>0.9967,0.0025,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0001,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.9956,0.0023,0.0010,0.0003</t>
-  </si>
-  <si>
-    <t>0.0004,0.0021,0.9994,0.0023</t>
+    <t>0.0004,0.9991,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0059,0.9941,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.9995,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0836,0.0003,0.8818,0.0040</t>
+  </si>
+  <si>
+    <t>0.0131,0.0002,0.9844,0.0004</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0079,0.0003,0.9907,0.0002</t>
+  </si>
+  <si>
+    <t>0.2009,0.0003,0.8463,0.0004</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9998,0.0002</t>
+  </si>
+  <si>
+    <t>0.0381,0.9615,0.0011,0.0011</t>
+  </si>
+  <si>
+    <t>0.1266,0.1384,0.6450,0.0016</t>
+  </si>
+  <si>
+    <t>0.0002,0.0035,0.9986,0.0582</t>
+  </si>
+  <si>
+    <t>0.0058,0.9842,0.0116,0.0004</t>
+  </si>
+  <si>
+    <t>0.9875,0.0030,0.0015,0.0022</t>
+  </si>
+  <si>
+    <t>0.9330,0.0144,0.0352,0.0029</t>
+  </si>
+  <si>
+    <t>0.2542,0.8130,0.0013,0.0000</t>
+  </si>
+  <si>
+    <t>0.0016,0.9862,0.1543,0.0005</t>
+  </si>
+  <si>
+    <t>0.0013,0.9626,0.0321,0.0120</t>
+  </si>
+  <si>
+    <t>0.0051,0.0005,0.9901,0.0010</t>
+  </si>
+  <si>
+    <t>0.0072,0.0028,0.9861,0.0003</t>
+  </si>
+  <si>
+    <t>0.0033,0.0001,0.9935,0.0008</t>
+  </si>
+  <si>
+    <t>0.0002,0.0176,0.9988,0.0001</t>
+  </si>
+  <si>
+    <t>0.0011,0.9948,0.0026,0.0007</t>
+  </si>
+  <si>
+    <t>0.0007,0.0003,0.9977,0.0006</t>
+  </si>
+  <si>
+    <t>0.0094,0.0691,0.0003,0.9781</t>
+  </si>
+  <si>
+    <t>0.0005,0.9982,0.0023,0.0006</t>
+  </si>
+  <si>
+    <t>0.0002,0.9976,0.0665,0.0005</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0013,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0007,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.0073,0.9970,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0006,0.0000,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0002,0.9993,0.0001</t>
+  </si>
+  <si>
+    <t>0.0016,0.0025,0.9960,0.0013</t>
+  </si>
+  <si>
+    <t>0.9025,0.1390,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9631,0.0285,0.0081,0.0008</t>
+  </si>
+  <si>
+    <t>0.0007,0.0006,0.9987,0.0054</t>
+  </si>
+  <si>
+    <t>0.9960,0.0044,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.8887,0.1505,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.9894,0.9747,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0003,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0036,0.9994,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9838,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9997,0.0004</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9997,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9900,0.0002,0.0123,0.0000</t>
+  </si>
+  <si>
+    <t>0.9444,0.0001,0.0916,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0009,0.9999,0.0011</t>
+  </si>
+  <si>
+    <t>0.0000,0.9964,0.9948,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9974,0.6718,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0103,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9995,0.9802,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.0001,0.0001,0.9996</t>
+  </si>
+  <si>
+    <t>0.0000,0.0004,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0032,0.0000,0.0004,0.9986</t>
+  </si>
+  <si>
+    <t>0.0002,0.0003,0.0002,0.9998</t>
+  </si>
+  <si>
+    <t>0.0001,0.9823,0.9605,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9967,0.4375,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9834,0.9686,0.0001</t>
+  </si>
+  <si>
+    <t>0.0011,0.0601,0.9781,0.0011</t>
+  </si>
+  <si>
+    <t>0.0000,0.9577,0.9985,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9991,0.0929,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0002,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0003,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9982,0.0010,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9994,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9990,0.0004,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9987,0.0011,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0005,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0012,0.0001,0.9986,0.0005</t>
+  </si>
+  <si>
+    <t>0.0002,0.0002,0.9995,0.0003</t>
+  </si>
+  <si>
+    <t>0.9472,0.0002,0.0345,0.0008</t>
+  </si>
+  <si>
+    <t>0.0011,0.0002,0.9990,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9995,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9991,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.9996,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0447,0.9685,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.5986,0.0062,0.2805,0.0016</t>
+  </si>
+  <si>
+    <t>0.3567,0.0008,0.6832,0.0002</t>
+  </si>
+  <si>
+    <t>0.4678,0.2582,0.0316,0.0016</t>
+  </si>
+  <si>
+    <t>0.2112,0.0391,0.5118,0.0039</t>
+  </si>
+  <si>
+    <t>0.0002,0.0079,0.0010,0.9991</t>
+  </si>
+  <si>
+    <t>0.0003,0.9989,0.0054,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0006</t>
+  </si>
+  <si>
+    <t>0.0000,0.9994,0.9488,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9494,0.0277,0.0079,0.0001</t>
+  </si>
+  <si>
+    <t>0.2935,0.7483,0.0024,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9991,0.0003,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9992,0.0002,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0517,0.9918,0.0017</t>
+  </si>
+  <si>
+    <t>0.0006,0.0669,0.9972,0.0000</t>
+  </si>
+  <si>
+    <t>0.0021,0.0253,0.9887,0.0004</t>
+  </si>
+  <si>
+    <t>0.0032,0.0012,0.9924,0.0004</t>
+  </si>
+  <si>
+    <t>0.9730,0.0019,0.0088,0.0005</t>
+  </si>
+  <si>
+    <t>0.9974,0.0003,0.0006,0.0003</t>
+  </si>
+  <si>
+    <t>0.0228,0.0006,0.9820,0.0005</t>
+  </si>
+  <si>
+    <t>0.9689,0.0006,0.0274,0.0002</t>
+  </si>
+  <si>
+    <t>0.0399,0.0000,0.0000,0.9907</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0012,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0001,0.9999</t>
+  </si>
+  <si>
+    <t>0.0000,0.9994,0.3783,0.0000</t>
+  </si>
+  <si>
+    <t>0.9983,0.0008,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0030,0.9934,0.0002,0.0045</t>
+  </si>
+  <si>
+    <t>0.9982,0.0004,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.0088,0.9905,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.5411,0.0006,0.0098,0.4261</t>
+  </si>
+  <si>
+    <t>0.0007,0.0015,0.9979,0.0022</t>
+  </si>
+  <si>
+    <t>0.9872,0.0001,0.0013,0.0094</t>
+  </si>
+  <si>
+    <t>0.9972,0.0003,0.0007,0.0008</t>
+  </si>
+  <si>
+    <t>0.0028,0.9951,0.0009,0.0005</t>
+  </si>
+  <si>
+    <t>0.9902,0.0038,0.0014,0.0005</t>
+  </si>
+  <si>
+    <t>0.9949,0.0002,0.0043,0.0001</t>
+  </si>
+  <si>
+    <t>0.4358,0.3414,0.0287,0.0020</t>
+  </si>
+  <si>
+    <t>0.9978,0.0003,0.0012,0.0000</t>
+  </si>
+  <si>
+    <t>0.3379,0.4958,0.0200,0.0011</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9990,0.0002,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9993,0.0002,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9937,0.0032,0.0005,0.0006</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9752,0.0262,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.2948,0.7930,0.0009,0.0000</t>
+  </si>
+  <si>
+    <t>0.9721,0.0384,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.1222,0.0064,0.9277,0.0002</t>
+  </si>
+  <si>
+    <t>0.9953,0.0044,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9991,0.0003,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9961,0.0030,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0004,0.9999,0.0002</t>
+  </si>
+  <si>
+    <t>0.9819,0.0089,0.0039,0.0006</t>
+  </si>
+  <si>
+    <t>0.0002,0.0002,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0009,0.0453,0.9961,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.0033,0.9983,0.0005</t>
+  </si>
+  <si>
+    <t>0.0014,0.0010,0.9988,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9998,0.0002</t>
+  </si>
+  <si>
+    <t>0.0059,0.0049,0.9806,0.0061</t>
+  </si>
+  <si>
+    <t>0.0037,0.0005,0.9964,0.0001</t>
+  </si>
+  <si>
+    <t>0.5898,0.0126,0.2403,0.0007</t>
+  </si>
+  <si>
+    <t>0.1238,0.0225,0.6706,0.0009</t>
+  </si>
+  <si>
+    <t>0.0311,0.0062,0.9526,0.0002</t>
+  </si>
+  <si>
+    <t>0.2376,0.0064,0.6815,0.0002</t>
+  </si>
+  <si>
+    <t>0.9185,0.0028,0.0574,0.0009</t>
+  </si>
+  <si>
+    <t>0.0088,0.0012,0.9883,0.0008</t>
+  </si>
+  <si>
+    <t>0.0504,0.9550,0.0020,0.0006</t>
+  </si>
+  <si>
+    <t>0.0017,0.9979,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0363,0.9706,0.0004,0.0006</t>
+  </si>
+  <si>
+    <t>0.8378,0.2023,0.0010,0.0004</t>
+  </si>
+  <si>
+    <t>0.0623,0.9466,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.8555,0.1303,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9987,0.0000,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9252,0.0144,0.0064,0.0036</t>
+  </si>
+  <si>
+    <t>0.5448,0.0050,0.5058,0.0003</t>
+  </si>
+  <si>
+    <t>0.8302,0.0011,0.1272,0.0043</t>
+  </si>
+  <si>
+    <t>0.0003,0.0007,0.9990,0.0039</t>
+  </si>
+  <si>
+    <t>0.0014,0.0101,0.9912,0.0019</t>
+  </si>
+  <si>
+    <t>0.0048,0.0103,0.9860,0.0008</t>
+  </si>
+  <si>
+    <t>0.0126,0.0009,0.9779,0.0020</t>
+  </si>
+  <si>
+    <t>0.0002,0.0046,0.9980,0.0011</t>
+  </si>
+  <si>
+    <t>0.9974,0.0003,0.0000,0.0004</t>
+  </si>
+  <si>
+    <t>0.9947,0.0025,0.0010,0.0003</t>
+  </si>
+  <si>
+    <t>0.9951,0.0028,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9972,0.0036,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9989,0.0008,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9999,0.0002</t>
+  </si>
+  <si>
+    <t>0.0010,0.0021,0.9981,0.0008</t>
+  </si>
+  <si>
+    <t>0.9543,0.0012,0.0327,0.0016</t>
+  </si>
+  <si>
+    <t>0.0003,0.0001,0.9993,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.0004,0.9992,0.0009</t>
+  </si>
+  <si>
+    <t>0.0000,0.3540,0.9984,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0002,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0008,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.0004,0.9982,0.0002</t>
+  </si>
+  <si>
+    <t>0.0015,0.0054,0.9954,0.0011</t>
+  </si>
+  <si>
+    <t>0.0426,0.0012,0.9350,0.0055</t>
+  </si>
+  <si>
+    <t>0.9046,0.0006,0.0748,0.0023</t>
+  </si>
+  <si>
+    <t>0.9993,0.0000,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9990,0.0007,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9969,0.0016,0.0006,0.0002</t>
   </si>
   <si>
     <t>0.9993,0.0004,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9674,0.0512,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9977,0.0017,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.3161,0.9963,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0004,0.9996,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.0004,0.9985,0.0006</t>
-  </si>
-  <si>
-    <t>0.0000,0.9732,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9998,0.0004</t>
-  </si>
-  <si>
-    <t>0.0001,0.9997,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9999,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.6703,0.0001,0.5861,0.0000</t>
-  </si>
-  <si>
-    <t>0.3347,0.0018,0.6877,0.0003</t>
-  </si>
-  <si>
-    <t>0.0002,0.0004,0.9994,0.0032</t>
-  </si>
-  <si>
-    <t>0.0000,0.9928,0.9315,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9980,0.8473,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9994,0.2925,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9987,0.9473,0.0000</t>
-  </si>
-  <si>
-    <t>0.0053,0.0000,0.0005,0.9978</t>
-  </si>
-  <si>
-    <t>0.0000,0.0006,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0008,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0012,0.0001,0.0007,0.9989</t>
-  </si>
-  <si>
-    <t>0.0004,0.0001,0.0007,0.9995</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9977,0.2613,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9983,0.9483,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9360,0.9781,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.6212,0.9957,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9302,0.9944,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9956,0.6472,0.0000</t>
-  </si>
-  <si>
-    <t>0.9980,0.0009,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9982,0.0013,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9983,0.0002,0.0000,0.0005</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9987,0.0003,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.9982,0.0013,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9997,0.0008</t>
-  </si>
-  <si>
-    <t>0.0005,0.0004,0.9987,0.0001</t>
-  </si>
-  <si>
-    <t>0.9902,0.0004,0.0013,0.0001</t>
-  </si>
-  <si>
-    <t>0.0014,0.0001,0.9986,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9996,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.9988,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0601,0.9524,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.2107,0.1210,0.3712,0.0027</t>
-  </si>
-  <si>
-    <t>0.9670,0.0004,0.0327,0.0001</t>
-  </si>
-  <si>
-    <t>0.7776,0.0233,0.0558,0.0017</t>
-  </si>
-  <si>
-    <t>0.6606,0.0705,0.0331,0.0048</t>
-  </si>
-  <si>
-    <t>0.0010,0.0171,0.0043,0.9952</t>
-  </si>
-  <si>
-    <t>0.0002,0.9993,0.0082,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0001,0.0090</t>
-  </si>
-  <si>
-    <t>0.0000,0.9997,0.9958,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.6583,0.3607,0.0039,0.0002</t>
-  </si>
-  <si>
-    <t>0.5825,0.4148,0.0055,0.0001</t>
-  </si>
-  <si>
-    <t>0.9967,0.0002,0.0023,0.0003</t>
-  </si>
-  <si>
-    <t>0.9991,0.0002,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9978,0.0009,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.9988,0.0002,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9978,0.0006,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.0003,0.5477,0.9828,0.0007</t>
-  </si>
-  <si>
-    <t>0.0006,0.5875,0.9850,0.0000</t>
-  </si>
-  <si>
-    <t>0.0020,0.0247,0.9899,0.0005</t>
-  </si>
-  <si>
-    <t>0.0016,0.0009,0.9957,0.0004</t>
-  </si>
-  <si>
-    <t>0.9967,0.0001,0.0011,0.0000</t>
-  </si>
-  <si>
-    <t>0.1081,0.0016,0.9203,0.0003</t>
-  </si>
-  <si>
-    <t>0.0176,0.0006,0.9841,0.0007</t>
-  </si>
-  <si>
-    <t>0.0765,0.0077,0.8921,0.0009</t>
-  </si>
-  <si>
-    <t>0.0014,0.0001,0.0000,0.9996</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0069,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0000,0.9970,0.9310,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0149,0.9775,0.0014,0.0062</t>
-  </si>
-  <si>
-    <t>0.9986,0.0004,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9428,0.0741,0.0008,0.0002</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0160,0.0002,0.0009,0.9937</t>
-  </si>
-  <si>
-    <t>0.0009,0.0041,0.9976,0.0028</t>
-  </si>
-  <si>
-    <t>0.9419,0.0002,0.0248,0.0067</t>
-  </si>
-  <si>
-    <t>0.9982,0.0003,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.2792,0.7794,0.0007,0.0006</t>
-  </si>
-  <si>
-    <t>0.9738,0.0069,0.0055,0.0020</t>
-  </si>
-  <si>
-    <t>0.9969,0.0001,0.0026,0.0001</t>
-  </si>
-  <si>
-    <t>0.9375,0.0336,0.0040,0.0004</t>
-  </si>
-  <si>
-    <t>0.9894,0.0016,0.0053,0.0001</t>
-  </si>
-  <si>
-    <t>0.7935,0.1193,0.0123,0.0009</t>
-  </si>
-  <si>
-    <t>0.9988,0.0002,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9983,0.0005,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9995,0.0000,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9884,0.0064,0.0013,0.0010</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9405,0.0577,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.2667,0.8206,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.5087,0.5611,0.0008,0.0004</t>
-  </si>
-  <si>
-    <t>0.0022,0.0035,0.9978,0.0003</t>
-  </si>
-  <si>
-    <t>0.9915,0.0053,0.0001,0.0006</t>
-  </si>
-  <si>
-    <t>0.9972,0.0011,0.0001,0.0006</t>
-  </si>
-  <si>
-    <t>0.9990,0.0002,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.0007,0.9999,0.0003</t>
-  </si>
-  <si>
-    <t>0.9820,0.0111,0.0020,0.0006</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0013,0.0273,0.9954,0.0004</t>
-  </si>
-  <si>
-    <t>0.0004,0.0001,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0117,0.9972,0.0005</t>
-  </si>
-  <si>
-    <t>0.0001,0.0003,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0002</t>
-  </si>
-  <si>
-    <t>0.0037,0.0008,0.9955,0.0002</t>
-  </si>
-  <si>
-    <t>0.0789,0.0003,0.9605,0.0001</t>
-  </si>
-  <si>
-    <t>0.0406,0.0063,0.9040,0.0063</t>
-  </si>
-  <si>
-    <t>0.8749,0.0005,0.1796,0.0000</t>
-  </si>
-  <si>
-    <t>0.0470,0.1033,0.6493,0.0010</t>
-  </si>
-  <si>
-    <t>0.8253,0.0023,0.1644,0.0001</t>
-  </si>
-  <si>
-    <t>0.9806,0.0007,0.0086,0.0004</t>
-  </si>
-  <si>
-    <t>0.3541,0.0032,0.5992,0.0013</t>
-  </si>
-  <si>
-    <t>0.0088,0.9910,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.0055,0.9935,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.0309,0.9746,0.0007,0.0006</t>
-  </si>
-  <si>
-    <t>0.9021,0.1230,0.0011,0.0002</t>
-  </si>
-  <si>
-    <t>0.0748,0.9426,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9888,0.0082,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9960,0.0001,0.0012,0.0001</t>
-  </si>
-  <si>
-    <t>0.9465,0.0120,0.0089,0.0020</t>
-  </si>
-  <si>
-    <t>0.1048,0.0026,0.9149,0.0004</t>
-  </si>
-  <si>
-    <t>0.5941,0.0003,0.4141,0.0031</t>
-  </si>
-  <si>
-    <t>0.0020,0.0008,0.9942,0.0154</t>
-  </si>
-  <si>
-    <t>0.0004,0.0028,0.9986,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.0008,0.9990,0.0001</t>
-  </si>
-  <si>
-    <t>0.0635,0.0103,0.8694,0.0028</t>
-  </si>
-  <si>
-    <t>0.0002,0.1004,0.9950,0.0005</t>
-  </si>
-  <si>
-    <t>0.9928,0.0022,0.0000,0.0006</t>
-  </si>
-  <si>
-    <t>0.9993,0.0002,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9988,0.0004,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9979,0.0020,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9969,0.0012,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.9986,0.0011,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9964,0.0011,0.0002,0.0008</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0719,0.0487,0.7838,0.0009</t>
-  </si>
-  <si>
-    <t>0.9725,0.0013,0.0172,0.0013</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9996,0.0001</t>
-  </si>
-  <si>
-    <t>0.0007,0.0023,0.9975,0.0020</t>
-  </si>
-  <si>
-    <t>0.0001,0.0330,0.9986,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0003,0.9996,0.0002</t>
-  </si>
-  <si>
-    <t>0.0028,0.0018,0.9926,0.0004</t>
-  </si>
-  <si>
-    <t>0.0014,0.0028,0.9960,0.0026</t>
-  </si>
-  <si>
-    <t>0.2650,0.0007,0.7455,0.0009</t>
-  </si>
-  <si>
-    <t>0.0541,0.0001,0.9560,0.0006</t>
-  </si>
-  <si>
-    <t>0.9993,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0005,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9990,0.0007,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0142,0.0027,0.9735,0.0005</t>
-  </si>
-  <si>
-    <t>0.0000,0.0009,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0008,0.9996,0.0001</t>
-  </si>
-  <si>
-    <t>0.0042,0.0131,0.9887,0.0007</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0476,0.0015,0.9484,0.0009</t>
-  </si>
-  <si>
-    <t>0.0056,0.0029,0.9883,0.0020</t>
-  </si>
-  <si>
-    <t>0.0153,0.0015,0.9622,0.0066</t>
-  </si>
-  <si>
-    <t>0.9992,0.0000,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.0005,0.0012,0.0000,0.9997</t>
-  </si>
-  <si>
-    <t>0.0090,0.0001,0.0002,0.9975</t>
-  </si>
-  <si>
-    <t>0.8125,0.0005,0.0005,0.1628</t>
+    <t>0.9991,0.0005,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0097,0.0011,0.9879,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.0003,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0058,0.9975,0.0004</t>
+  </si>
+  <si>
+    <t>0.0009,0.0219,0.9946,0.0010</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.0044,0.0008,0.9863,0.0043</t>
+  </si>
+  <si>
+    <t>0.0069,0.0061,0.9804,0.0038</t>
+  </si>
+  <si>
+    <t>0.0668,0.0010,0.9053,0.0025</t>
+  </si>
+  <si>
+    <t>0.9995,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0020,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0044,0.0004,0.0003,0.9979</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.1679,0.0007,0.0024,0.8913</t>
   </si>
 </sst>
 </file>
@@ -1875,7 +1887,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1889,7 +1901,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1903,7 +1915,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1917,7 +1929,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1931,7 +1943,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1945,7 +1957,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1959,7 +1971,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1973,7 +1985,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1987,7 +1999,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2001,7 +2013,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2015,7 +2027,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2029,7 +2041,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2043,7 +2055,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2057,7 +2069,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2068,10 +2080,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D16" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2085,7 +2097,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2099,7 +2111,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2113,7 +2125,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2127,7 +2139,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2141,7 +2153,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2155,7 +2167,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2169,7 +2181,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2292,7 +2304,7 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D32" t="s">
         <v>293</v>
@@ -2362,7 +2374,7 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D37" t="s">
         <v>298</v>
@@ -2390,7 +2402,7 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D39" t="s">
         <v>300</v>
@@ -2488,7 +2500,7 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
         <v>307</v>
@@ -2645,7 +2657,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>318</v>
+        <v>271</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2659,7 +2671,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2673,7 +2685,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2687,7 +2699,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>321</v>
+        <v>271</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2701,7 +2713,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2715,7 +2727,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2726,10 +2738,10 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2743,7 +2755,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2757,7 +2769,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2771,7 +2783,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2785,7 +2797,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2799,7 +2811,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2813,7 +2825,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2824,10 +2836,10 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2838,10 +2850,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2855,7 +2867,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2869,7 +2881,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2883,7 +2895,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2897,7 +2909,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2911,7 +2923,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2925,7 +2937,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2939,7 +2951,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2953,7 +2965,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2967,7 +2979,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2981,7 +2993,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2995,7 +3007,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>343</v>
+        <v>267</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3006,10 +3018,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3020,10 +3032,10 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D84" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3037,7 +3049,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3048,10 +3060,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3065,7 +3077,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3076,10 +3088,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D88" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3093,7 +3105,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>272</v>
+        <v>347</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3107,7 +3119,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3121,7 +3133,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3135,7 +3147,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3149,7 +3161,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3163,7 +3175,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3177,7 +3189,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3191,7 +3203,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3205,7 +3217,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3219,7 +3231,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>357</v>
+        <v>271</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3247,7 +3259,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>357</v>
+        <v>271</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3261,7 +3273,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>358</v>
+        <v>271</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3275,7 +3287,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>269</v>
+        <v>355</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3289,7 +3301,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3303,7 +3315,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3317,7 +3329,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3331,7 +3343,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3345,7 +3357,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3359,7 +3371,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3373,7 +3385,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3387,7 +3399,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3401,7 +3413,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3415,7 +3427,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3429,7 +3441,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>280</v>
+        <v>363</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3443,7 +3455,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3457,7 +3469,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3471,7 +3483,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3482,10 +3494,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3496,10 +3508,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D118" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3510,10 +3522,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3527,7 +3539,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3541,7 +3553,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3555,7 +3567,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>284</v>
+        <v>372</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3569,7 +3581,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3583,7 +3595,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3597,7 +3609,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3611,7 +3623,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3622,10 +3634,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3639,7 +3651,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3653,7 +3665,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>358</v>
+        <v>275</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3667,7 +3679,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>274</v>
+        <v>378</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3695,7 +3707,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>380</v>
+        <v>350</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3709,7 +3721,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3723,7 +3735,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3737,7 +3749,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3748,10 +3760,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3762,10 +3774,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3779,7 +3791,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3793,7 +3805,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3807,7 +3819,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3818,10 +3830,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3835,7 +3847,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3846,10 +3858,10 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3863,7 +3875,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3877,7 +3889,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3891,7 +3903,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3905,7 +3917,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3916,10 +3928,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D148" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3933,7 +3945,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3947,7 +3959,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3961,7 +3973,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3972,10 +3984,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3989,7 +4001,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4000,10 +4012,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4017,7 +4029,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4031,7 +4043,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4045,7 +4057,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4059,7 +4071,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4073,7 +4085,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4087,7 +4099,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4101,7 +4113,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4112,10 +4124,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D162" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4129,7 +4141,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4140,10 +4152,10 @@
         <v>259</v>
       </c>
       <c r="C164" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D164" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4157,7 +4169,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>270</v>
+        <v>411</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4171,7 +4183,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>412</v>
+        <v>271</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4185,7 +4197,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4199,7 +4211,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4213,7 +4225,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4227,7 +4239,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4241,7 +4253,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4255,7 +4267,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4269,7 +4281,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4283,7 +4295,7 @@
         <v>262</v>
       </c>
       <c r="D174" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4294,10 +4306,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4311,7 +4323,7 @@
         <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4325,7 +4337,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4339,7 +4351,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4353,7 +4365,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>401</v>
+        <v>423</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4367,7 +4379,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4381,7 +4393,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4395,7 +4407,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4409,7 +4421,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4423,7 +4435,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4437,7 +4449,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4451,7 +4463,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4465,7 +4477,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4479,7 +4491,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>433</v>
+        <v>290</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4493,7 +4505,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4507,7 +4519,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4521,7 +4533,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4532,10 +4544,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4546,10 +4558,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4563,7 +4575,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4574,10 +4586,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D195" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4591,7 +4603,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4605,7 +4617,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4619,7 +4631,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4633,7 +4645,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4647,7 +4659,7 @@
         <v>262</v>
       </c>
       <c r="D200" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4661,7 +4673,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4675,7 +4687,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4689,7 +4701,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4703,7 +4715,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4717,7 +4729,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4728,10 +4740,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D206" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4745,7 +4757,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4759,7 +4771,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4773,7 +4785,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4787,7 +4799,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4801,7 +4813,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4815,7 +4827,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4829,7 +4841,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4843,7 +4855,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4857,7 +4869,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4871,7 +4883,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4885,7 +4897,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4899,7 +4911,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4913,7 +4925,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4927,7 +4939,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4941,7 +4953,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4955,7 +4967,7 @@
         <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4969,7 +4981,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4983,7 +4995,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4997,7 +5009,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5011,7 +5023,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5025,7 +5037,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>433</v>
+        <v>469</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5039,7 +5051,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5053,7 +5065,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>433</v>
+        <v>471</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5106,7 +5118,7 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D233" t="s">
         <v>475</v>
@@ -5123,7 +5135,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>274</v>
+        <v>476</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5137,7 +5149,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5151,7 +5163,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>358</v>
+        <v>478</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5165,7 +5177,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5179,7 +5191,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>358</v>
+        <v>480</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5193,7 +5205,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>478</v>
+        <v>461</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5207,7 +5219,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>272</v>
+        <v>481</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5221,7 +5233,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5235,7 +5247,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>357</v>
+        <v>271</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5249,7 +5261,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5263,7 +5275,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5277,7 +5289,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5291,7 +5303,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5305,7 +5317,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5319,7 +5331,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5333,7 +5345,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5347,7 +5359,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5361,7 +5373,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5375,7 +5387,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5389,7 +5401,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5403,7 +5415,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5417,7 +5429,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>393</v>
+        <v>494</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5428,10 +5440,10 @@
         <v>259</v>
       </c>
       <c r="C256" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D256" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
     </row>
   </sheetData>
